--- a/results/0_excel_files/statistical_analysis_0_file_size_TEST_0.xlsx
+++ b/results/0_excel_files/statistical_analysis_0_file_size_TEST_0.xlsx
@@ -8,14 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Bakalaura Darbs\!Code\Bakalaura_darbs\results\0_excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{20B3539F-F4FC-4A88-8EAB-FDA29E912C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E3B711-6A21-47D1-AD20-95D2652CA53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31840CB6-00E6-4A31-9D2B-9D4B8597FC34}"/>
   </bookViews>
   <sheets>
     <sheet name="TEST_0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">(TEST_0!$B$2,TEST_0!$B$9,TEST_0!$B$16,TEST_0!$B$23,TEST_0!$B$30)</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">(TEST_0!$C$4,TEST_0!$C$11,TEST_0!$C$18,TEST_0!$C$25,TEST_0!$C$32)</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -615,6 +632,1324 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>TEST_0!$B$1</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>TEST_0</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>TEST_0!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Document file size (KB)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>(TEST_0!$B$5,TEST_0!$B$12,TEST_0!$B$19,TEST_0!$B$26,TEST_0!$B$33)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.46</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.36</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-739F-4D94-AEE2-15D11CF68E07}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="955316968"/>
+        <c:axId val="955316248"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Document file size change (%)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(TEST_0!$B$2,TEST_0!$B$9,TEST_0!$B$16,TEST_0!$B$23,TEST_0!$B$30)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>clean</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hide_in_text</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>modify_RGB_color_ch</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>unispace</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>unicode_homoglyphs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(TEST_0!$C$5,TEST_0!$C$12,TEST_0!$C$19,TEST_0!$C$26,TEST_0!$C$33)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96.26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>92.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.82</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>92.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-739F-4D94-AEE2-15D11CF68E07}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="898786888"/>
+        <c:axId val="898783288"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="955316968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:strRef>
+              <c:f>TEST_0!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Data set</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="955316248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="955316248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="18"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:strRef>
+              <c:f>TEST_0!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Document file size (KB)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="955316968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="898783288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="115"/>
+          <c:min val="85"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Document file size change (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="898786888"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="898786888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="898783288"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA87DCD9-12CF-449A-397B-69E55A075EBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -934,14 +2269,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85167A97-8134-4D52-B412-27B4B9641F31}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -949,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -957,7 +2292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -965,23 +2300,31 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>17511</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <f>ROUND(B4 / B4 * 100, 2)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <v>17.100000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <f>ROUND(B5 / B5 * 100, 2)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -989,7 +2332,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -997,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1005,7 +2348,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1013,23 +2356,31 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11">
-        <v>16897</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16851</v>
+      </c>
+      <c r="C11">
+        <f>ROUND(B11 / B4 * 100, 2)</f>
+        <v>96.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16.46</v>
+      </c>
+      <c r="C12">
+        <f>ROUND(B12 / B5 * 100, 2)</f>
+        <v>96.26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1037,7 +2388,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -1053,7 +2404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1061,23 +2412,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
       <c r="B18">
-        <v>16187</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16148</v>
+      </c>
+      <c r="C18">
+        <f>ROUND(B18 / B4 * 100, 2)</f>
+        <v>92.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
       <c r="B19">
-        <v>15.81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.77</v>
+      </c>
+      <c r="C19">
+        <f>ROUND(B19 / B5 * 100, 2)</f>
+        <v>92.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1085,7 +2444,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1093,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -1101,39 +2460,47 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
       <c r="B25">
-        <v>15747</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15729</v>
+      </c>
+      <c r="C25">
+        <f>ROUND(B25 / B4 * 100, 2)</f>
+        <v>89.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
       <c r="B26">
-        <v>15.38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.36</v>
+      </c>
+      <c r="C26">
+        <f>ROUND(B26 / B5 * 100, 2)</f>
+        <v>89.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
       <c r="B27">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>2</v>
       </c>
@@ -1149,7 +2516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1157,23 +2524,31 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32">
-        <v>16211</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16116</v>
+      </c>
+      <c r="C32">
+        <f>ROUND(B32 / B4 * 100, 2)</f>
+        <v>92.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
       <c r="B33">
-        <v>15.83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.74</v>
+      </c>
+      <c r="C33">
+        <f>ROUND(B33 / B5 * 100, 2)</f>
+        <v>92.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1183,5 +2558,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>